--- a/python-excel-unmatched-items-demo.xlsx
+++ b/python-excel-unmatched-items-demo.xlsx
@@ -8,12 +8,13 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\georg\Documents\GitHub\blog-files\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{737352AA-3848-49C6-BEE4-B76C125C2C9E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EC976357-0454-4755-9AF7-EAEB336E497A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-93" yWindow="-93" windowWidth="16826" windowHeight="11280" xr2:uid="{8FF3E024-BCDF-426A-AAE8-34C49D3414E0}"/>
+    <workbookView xWindow="-93" yWindow="-93" windowWidth="16826" windowHeight="11280" activeTab="1" xr2:uid="{8FF3E024-BCDF-426A-AAE8-34C49D3414E0}"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="data" sheetId="1" r:id="rId1"/>
+    <sheet name="demo" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -36,6 +37,179 @@
     </ext>
   </extLst>
 </workbook>
+</file>
+
+<file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
+<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
+  <metadataTypes count="2">
+    <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
+    <metadataType name="XLRICHVALUE" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1"/>
+  </metadataTypes>
+  <futureMetadata name="XLDAPR" count="1">
+    <bk>
+      <extLst>
+        <ext uri="{bdbb8cdc-fa1e-496e-a857-3c3f30c029c3}">
+          <xda:dynamicArrayProperties fDynamic="1" fCollapsed="0"/>
+        </ext>
+      </extLst>
+    </bk>
+  </futureMetadata>
+  <futureMetadata name="XLRICHVALUE" count="10">
+    <bk>
+      <extLst>
+        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
+          <xlrd:rvb i="5"/>
+        </ext>
+      </extLst>
+    </bk>
+    <bk>
+      <extLst>
+        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
+          <xlrd:rvb i="6"/>
+        </ext>
+      </extLst>
+    </bk>
+    <bk>
+      <extLst>
+        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
+          <xlrd:rvb i="7"/>
+        </ext>
+      </extLst>
+    </bk>
+    <bk>
+      <extLst>
+        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
+          <xlrd:rvb i="8"/>
+        </ext>
+      </extLst>
+    </bk>
+    <bk>
+      <extLst>
+        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
+          <xlrd:rvb i="0"/>
+        </ext>
+      </extLst>
+    </bk>
+    <bk>
+      <extLst>
+        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
+          <xlrd:rvb i="9"/>
+        </ext>
+      </extLst>
+    </bk>
+    <bk>
+      <extLst>
+        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
+          <xlrd:rvb i="10"/>
+        </ext>
+      </extLst>
+    </bk>
+    <bk>
+      <extLst>
+        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
+          <xlrd:rvb i="1"/>
+        </ext>
+      </extLst>
+    </bk>
+    <bk>
+      <extLst>
+        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
+          <xlrd:rvb i="11"/>
+        </ext>
+      </extLst>
+    </bk>
+    <bk>
+      <extLst>
+        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
+          <xlrd:rvb i="2"/>
+        </ext>
+      </extLst>
+    </bk>
+  </futureMetadata>
+  <cellMetadata count="1">
+    <bk>
+      <rc t="1" v="0"/>
+    </bk>
+  </cellMetadata>
+  <valueMetadata count="10">
+    <bk>
+      <rc t="2" v="0"/>
+    </bk>
+    <bk>
+      <rc t="2" v="1"/>
+    </bk>
+    <bk>
+      <rc t="2" v="2"/>
+    </bk>
+    <bk>
+      <rc t="2" v="3"/>
+    </bk>
+    <bk>
+      <rc t="2" v="4"/>
+    </bk>
+    <bk>
+      <rc t="2" v="5"/>
+    </bk>
+    <bk>
+      <rc t="2" v="6"/>
+    </bk>
+    <bk>
+      <rc t="2" v="7"/>
+    </bk>
+    <bk>
+      <rc t="2" v="8"/>
+    </bk>
+    <bk>
+      <rc t="2" v="9"/>
+    </bk>
+  </valueMetadata>
+</metadata>
+</file>
+
+<file path=xl/python.xml><?xml version="1.0" encoding="utf-8"?>
+<python xmlns="http://schemas.microsoft.com/office/spreadsheetml/2023/python">
+  <environmentDefinition id="{882DD1B0-6546-4DFA-8A08-902A380B44EA}">
+    <initialization>
+      <code xml:space="preserve">import numpy as np
+import pandas as pd
+import matplotlib.pyplot as plt
+import seaborn as sns
+import statsmodels as sm
+import excel
+import warnings
+warnings.simplefilter('ignore')
+excel.set_xl_scalar_conversion(excel.convert_to_scalar)
+excel.set_xl_array_conversion(excel.convert_to_dataframe)
+</code>
+    </initialization>
+  </environmentDefinition>
+  <pythonScripts>
+    <pythonScript>
+      <code>invoices_df = xl(%P2%, headers=True)
+payments_df = xl(%P3%, headers=True)</code>
+    </pythonScript>
+    <pythonScript>
+      <code>unpaid_invoices = invoices_df[
+    ~invoices_df["Invoice"].isin(payments_df["Invoice"])
+]
+unpaid_invoices</code>
+    </pythonScript>
+    <pythonScript>
+      <code>comparison = invoices_df.merge(
+    payments_df,
+    on="Invoice",
+    how="outer",
+    indicator=True,
+    suffixes=("_invoice", "_payment")
+)
+comparison</code>
+    </pythonScript>
+    <pythonScript>
+      <code>unmatched = comparison.query('_merge != "both"')
+unmatched</code>
+    </pythonScript>
+  </pythonScripts>
+</python>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
@@ -159,6 +333,17 @@
   </cellStyles>
   <dxfs count="9">
     <dxf>
+      <numFmt numFmtId="3" formatCode="#,##0"/>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="19" formatCode="m/d/yyyy"/>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
@@ -167,6 +352,9 @@
     </dxf>
     <dxf>
       <numFmt numFmtId="19" formatCode="m/d/yyyy"/>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
@@ -191,20 +379,6 @@
       </font>
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
-    <dxf>
-      <numFmt numFmtId="3" formatCode="#,##0"/>
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="19" formatCode="m/d/yyyy"/>
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
@@ -218,26 +392,242 @@
 </styleSheet>
 </file>
 
+<file path=xl/richData/rdRichValueTypes.xml><?xml version="1.0" encoding="utf-8"?>
+<rvTypesInfo xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" mc:Ignorable="x">
+  <global>
+    <keyFlags>
+      <key name="_Self">
+        <flag name="ExcludeFromFile" value="1"/>
+        <flag name="ExcludeFromCalcComparison" value="1"/>
+      </key>
+      <key name="_DisplayString">
+        <flag name="ExcludeFromCalcComparison" value="1"/>
+      </key>
+      <key name="_Flags">
+        <flag name="ExcludeFromCalcComparison" value="1"/>
+      </key>
+      <key name="_Format">
+        <flag name="ExcludeFromCalcComparison" value="1"/>
+      </key>
+      <key name="_SubLabel">
+        <flag name="ExcludeFromCalcComparison" value="1"/>
+      </key>
+      <key name="_Attribution">
+        <flag name="ExcludeFromCalcComparison" value="1"/>
+      </key>
+      <key name="_Icon">
+        <flag name="ExcludeFromCalcComparison" value="1"/>
+      </key>
+      <key name="_Display">
+        <flag name="ExcludeFromCalcComparison" value="1"/>
+      </key>
+      <key name="_CanonicalPropertyNames">
+        <flag name="ExcludeFromCalcComparison" value="1"/>
+      </key>
+      <key name="_ClassificationId">
+        <flag name="ExcludeFromCalcComparison" value="1"/>
+      </key>
+    </keyFlags>
+  </global>
+</rvTypesInfo>
+</file>
+
+<file path=xl/richData/rdarray.xml><?xml version="1.0" encoding="utf-8"?>
+<arrayData xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" count="1">
+  <a r="6" c="4">
+    <v t="s"/>
+    <v t="s">Invoice</v>
+    <v t="s">Payment_Date</v>
+    <v t="s">Amount_Paid</v>
+    <v>0</v>
+    <v t="s">INV-1001</v>
+    <v t="r">0</v>
+    <v>1250</v>
+    <v>1</v>
+    <v t="s">INV-1002</v>
+    <v t="r">0</v>
+    <v>3400</v>
+    <v>2</v>
+    <v t="s">INV-1004</v>
+    <v t="r">1</v>
+    <v>2100</v>
+    <v>3</v>
+    <v t="s">INV-1006</v>
+    <v t="r">2</v>
+    <v>620</v>
+    <v>4</v>
+    <v t="s">INV-1007</v>
+    <v t="r">2</v>
+    <v>1475</v>
+  </a>
+</arrayData>
+</file>
+
+<file path=xl/richData/rdrichvalue.xml><?xml version="1.0" encoding="utf-8"?>
+<rvData xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" count="12">
+  <rv s="0">
+    <fb>46213</fb>
+    <v>2</v>
+  </rv>
+  <rv s="0">
+    <fb>46215</fb>
+    <v>2</v>
+  </rv>
+  <rv s="0">
+    <fb>46217</fb>
+    <v>2</v>
+  </rv>
+  <rv s="1">
+    <v>0</v>
+  </rv>
+  <rv s="2">
+    <v>DataFrame</v>
+    <v>1</v>
+    <v>3</v>
+  </rv>
+  <rv s="3">
+    <v>&lt;class 'pandas.core.frame.DataFrame'&gt;</v>
+    <v>DataFrame</v>
+    <v xml:space="preserve">    Invoice Payment_Date  Amount_Paid
+0  INV-1001   2026-07-10         1250
+1  INV-1002   2026-07-10         3400
+2  INV-1004   2026-07-12         2100
+3  INV-1006   2026-07-14          620
+4  INV-1007   2026-07-14         1475</v>
+    <v>4</v>
+    <v>3</v>
+  </rv>
+  <rv s="0">
+    <fb>46206</fb>
+    <v>2</v>
+  </rv>
+  <rv s="0">
+    <fb>46210</fb>
+    <v>2</v>
+  </rv>
+  <rv s="0">
+    <fb>46204</fb>
+    <v>2</v>
+  </rv>
+  <rv s="0">
+    <fb>46205</fb>
+    <v>2</v>
+  </rv>
+  <rv s="0">
+    <fb>46208</fb>
+    <v>2</v>
+  </rv>
+  <rv s="0">
+    <fb>46211</fb>
+    <v>2</v>
+  </rv>
+</rvData>
+</file>
+
+<file path=xl/richData/rdrichvaluestructure.xml><?xml version="1.0" encoding="utf-8"?>
+<rvStructures xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" count="4">
+  <s t="_formattednumber">
+    <k n="_Format" t="spb"/>
+  </s>
+  <s t="_array">
+    <k n="array" t="a"/>
+  </s>
+  <s t="_entity">
+    <k n="_DisplayString" t="s"/>
+    <k n="_ViewInfo" t="spb"/>
+    <k n="arrayPreview" t="r"/>
+  </s>
+  <s t="_python">
+    <k n="Python_type" t="s"/>
+    <k n="Python_typeName" t="s"/>
+    <k n="Python_str" t="s"/>
+    <k n="preview" t="r"/>
+    <k n="_Provider" t="spb"/>
+  </s>
+</rvStructures>
+</file>
+
+<file path=xl/richData/rdsupportingpropertybag.xml><?xml version="1.0" encoding="utf-8"?>
+<supportingPropertyBags xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2">
+  <spbData count="4">
+    <spb s="0">
+      <v>5</v>
+      <v>3</v>
+      <v>DataFrame</v>
+      <v>arrayPreview</v>
+      <v>1</v>
+    </spb>
+    <spb s="1">
+      <v>0</v>
+    </spb>
+    <spb s="2">
+      <v>1</v>
+    </spb>
+    <spb s="3">
+      <v>https://www.anaconda.com/excel</v>
+      <v>https://res.cdn.office.net/officepysvc/prod-service/anacondalogo.png</v>
+      <v>Python provided by Anaconda</v>
+    </spb>
+  </spbData>
+</supportingPropertyBags>
+</file>
+
+<file path=xl/richData/rdsupportingpropertybagstructure.xml><?xml version="1.0" encoding="utf-8"?>
+<spbStructures xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" count="4">
+  <s>
+    <k n="drw" t="i"/>
+    <k n="dcol" t="i"/>
+    <k n="name" t="s"/>
+    <k n="array" t="s"/>
+    <k n="headers" t="b"/>
+  </s>
+  <s>
+    <k n="ArrayCardInfo" t="spb"/>
+  </s>
+  <s>
+    <k n="_Self" t="i"/>
+  </s>
+  <s>
+    <k n="link" t="s"/>
+    <k n="logo" t="s"/>
+    <k n="name" t="s"/>
+  </s>
+</spbStructures>
+</file>
+
+<file path=xl/richData/richStyles.xml><?xml version="1.0" encoding="utf-8"?>
+<richStyleSheet xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" mc:Ignorable="x">
+  <dxfs count="1">
+    <x:dxf>
+      <x:numFmt numFmtId="19" formatCode="m/d/yyyy"/>
+    </x:dxf>
+  </dxfs>
+  <richStyles>
+    <rSty dxfid="0"/>
+  </richStyles>
+</richStyleSheet>
+</file>
+
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{AA014C78-6D47-4844-8FFA-EDD623912D86}" name="invoices" displayName="invoices" ref="A1:D7" totalsRowShown="0" headerRowDxfId="4">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{AA014C78-6D47-4844-8FFA-EDD623912D86}" name="invoices" displayName="invoices" ref="A1:D7" totalsRowShown="0" headerRowDxfId="8">
   <autoFilter ref="A1:D7" xr:uid="{AA014C78-6D47-4844-8FFA-EDD623912D86}"/>
   <tableColumns count="4">
-    <tableColumn id="1" xr3:uid="{BC3024B0-A9C8-4D51-892F-4803AB44E20B}" name="Invoice" dataDxfId="8"/>
-    <tableColumn id="2" xr3:uid="{04F4BDD1-5EED-452C-BAA2-CA37876D17E4}" name="Vendor" dataDxfId="7"/>
-    <tableColumn id="3" xr3:uid="{5DE38EE7-92AF-4A52-9E14-026367181210}" name="Invoice_Date" dataDxfId="6"/>
-    <tableColumn id="4" xr3:uid="{DD4B00F2-EBFF-4B63-B976-1417D98FAA82}" name="Amount" dataDxfId="5"/>
+    <tableColumn id="1" xr3:uid="{BC3024B0-A9C8-4D51-892F-4803AB44E20B}" name="Invoice" dataDxfId="7"/>
+    <tableColumn id="2" xr3:uid="{04F4BDD1-5EED-452C-BAA2-CA37876D17E4}" name="Vendor" dataDxfId="6"/>
+    <tableColumn id="3" xr3:uid="{5DE38EE7-92AF-4A52-9E14-026367181210}" name="Invoice_Date" dataDxfId="5"/>
+    <tableColumn id="4" xr3:uid="{DD4B00F2-EBFF-4B63-B976-1417D98FAA82}" name="Amount" dataDxfId="4"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{D9B63AC9-C4B6-40A0-A1B8-6A289FA2E9B6}" name="payments" displayName="payments" ref="F1:H6" totalsRowShown="0" headerRowDxfId="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{D9B63AC9-C4B6-40A0-A1B8-6A289FA2E9B6}" name="payments" displayName="payments" ref="F1:H6" totalsRowShown="0" headerRowDxfId="3">
   <autoFilter ref="F1:H6" xr:uid="{D9B63AC9-C4B6-40A0-A1B8-6A289FA2E9B6}"/>
   <tableColumns count="3">
-    <tableColumn id="1" xr3:uid="{DB4B351C-EAE2-4875-80C0-78B3BE1AF602}" name="Invoice" dataDxfId="3"/>
-    <tableColumn id="2" xr3:uid="{8A2C7CC3-D3C5-4A3C-BBA3-2342181E1624}" name="Payment_Date" dataDxfId="2"/>
-    <tableColumn id="3" xr3:uid="{C8D98C83-23F3-48FB-A01A-AC9054EBC8D9}" name="Amount_Paid" dataDxfId="1"/>
+    <tableColumn id="1" xr3:uid="{DB4B351C-EAE2-4875-80C0-78B3BE1AF602}" name="Invoice" dataDxfId="2"/>
+    <tableColumn id="2" xr3:uid="{8A2C7CC3-D3C5-4A3C-BBA3-2342181E1624}" name="Payment_Date" dataDxfId="1"/>
+    <tableColumn id="3" xr3:uid="{C8D98C83-23F3-48FB-A01A-AC9054EBC8D9}" name="Amount_Paid" dataDxfId="0"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -727,4 +1117,368 @@
     <tablePart r:id="rId2"/>
   </tableParts>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EA13AC69-478D-4992-B957-9C8F400999E7}">
+  <dimension ref="A1:H19"/>
+  <sheetFormatPr defaultRowHeight="26.35" x14ac:dyDescent="0.9"/>
+  <cols>
+    <col min="2" max="3" width="17.06640625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="10.96484375" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="12.265625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="11.23046875" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:8" x14ac:dyDescent="0.9">
+      <c r="A1" t="e" cm="1" vm="1">
+        <f t="array" ref="A1">_xlfn._xlws.PY(0,1,invoices[#All],payments[#All])</f>
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.9">
+      <c r="A3" t="str" cm="1">
+        <f t="array" ref="A3:E5">_xlfn._xlws.PY(1,0)</f>
+        <v/>
+      </c>
+      <c r="B3" t="str">
+        <v>Invoice</v>
+      </c>
+      <c r="C3" t="str">
+        <v>Vendor</v>
+      </c>
+      <c r="D3" t="str">
+        <v>Invoice_Date</v>
+      </c>
+      <c r="E3" t="str">
+        <v>Amount</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.9">
+      <c r="A4">
+        <v>2</v>
+      </c>
+      <c r="B4" t="str">
+        <v>INV-1003</v>
+      </c>
+      <c r="C4" t="str">
+        <v>Summit Software</v>
+      </c>
+      <c r="D4" vm="2">
+        <v>46206</v>
+      </c>
+      <c r="E4">
+        <v>895</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.9">
+      <c r="A5">
+        <v>4</v>
+      </c>
+      <c r="B5" t="str">
+        <v>INV-1005</v>
+      </c>
+      <c r="C5" t="str">
+        <v>Keystone Equipment</v>
+      </c>
+      <c r="D5" vm="3">
+        <v>46210</v>
+      </c>
+      <c r="E5">
+        <v>4750</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.9">
+      <c r="A7" t="str" cm="1">
+        <f t="array" ref="A7:G14">_xlfn._xlws.PY(2,0)</f>
+        <v>Invoice</v>
+      </c>
+      <c r="B7" t="str">
+        <v>Vendor</v>
+      </c>
+      <c r="C7" t="str">
+        <v>Invoice_Date</v>
+      </c>
+      <c r="D7" t="str">
+        <v>Amount</v>
+      </c>
+      <c r="E7" t="str">
+        <v>Payment_Date</v>
+      </c>
+      <c r="F7" t="str">
+        <v>Amount_Paid</v>
+      </c>
+      <c r="G7" t="str">
+        <v>_merge</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.9">
+      <c r="A8" t="str">
+        <v>INV-1001</v>
+      </c>
+      <c r="B8" t="str">
+        <v>Apex Office Supply</v>
+      </c>
+      <c r="C8" vm="4">
+        <v>46204</v>
+      </c>
+      <c r="D8">
+        <v>1250</v>
+      </c>
+      <c r="E8" vm="5">
+        <v>46213</v>
+      </c>
+      <c r="F8">
+        <v>1250</v>
+      </c>
+      <c r="G8" t="str">
+        <v>both</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.9">
+      <c r="A9" t="str">
+        <v>INV-1002</v>
+      </c>
+      <c r="B9" t="str">
+        <v>Northstar Logistics</v>
+      </c>
+      <c r="C9" vm="6">
+        <v>46205</v>
+      </c>
+      <c r="D9">
+        <v>3400</v>
+      </c>
+      <c r="E9" vm="5">
+        <v>46213</v>
+      </c>
+      <c r="F9">
+        <v>3400</v>
+      </c>
+      <c r="G9" t="str">
+        <v>both</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" x14ac:dyDescent="0.9">
+      <c r="A10" t="str">
+        <v>INV-1003</v>
+      </c>
+      <c r="B10" t="str">
+        <v>Summit Software</v>
+      </c>
+      <c r="C10" vm="2">
+        <v>46206</v>
+      </c>
+      <c r="D10">
+        <v>895</v>
+      </c>
+      <c r="E10" t="e">
+        <v>#NUM!</v>
+      </c>
+      <c r="F10" t="e">
+        <v>#NUM!</v>
+      </c>
+      <c r="G10" t="str">
+        <v>left_only</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" x14ac:dyDescent="0.9">
+      <c r="A11" t="str">
+        <v>INV-1004</v>
+      </c>
+      <c r="B11" t="str">
+        <v>Harbor Consulting</v>
+      </c>
+      <c r="C11" vm="7">
+        <v>46208</v>
+      </c>
+      <c r="D11">
+        <v>2100</v>
+      </c>
+      <c r="E11" vm="8">
+        <v>46215</v>
+      </c>
+      <c r="F11">
+        <v>2100</v>
+      </c>
+      <c r="G11" t="str">
+        <v>both</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" x14ac:dyDescent="0.9">
+      <c r="A12" t="str">
+        <v>INV-1005</v>
+      </c>
+      <c r="B12" t="str">
+        <v>Keystone Equipment</v>
+      </c>
+      <c r="C12" vm="3">
+        <v>46210</v>
+      </c>
+      <c r="D12">
+        <v>4750</v>
+      </c>
+      <c r="E12" t="e">
+        <v>#NUM!</v>
+      </c>
+      <c r="F12" t="e">
+        <v>#NUM!</v>
+      </c>
+      <c r="G12" t="str">
+        <v>left_only</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" x14ac:dyDescent="0.9">
+      <c r="A13" t="str">
+        <v>INV-1006</v>
+      </c>
+      <c r="B13" t="str">
+        <v>Metro Utilities</v>
+      </c>
+      <c r="C13" vm="9">
+        <v>46211</v>
+      </c>
+      <c r="D13">
+        <v>620</v>
+      </c>
+      <c r="E13" vm="10">
+        <v>46217</v>
+      </c>
+      <c r="F13">
+        <v>620</v>
+      </c>
+      <c r="G13" t="str">
+        <v>both</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" x14ac:dyDescent="0.9">
+      <c r="A14" t="str">
+        <v>INV-1007</v>
+      </c>
+      <c r="B14" t="e">
+        <v>#NUM!</v>
+      </c>
+      <c r="C14" t="e">
+        <v>#NUM!</v>
+      </c>
+      <c r="D14" t="e">
+        <v>#NUM!</v>
+      </c>
+      <c r="E14" vm="10">
+        <v>46217</v>
+      </c>
+      <c r="F14">
+        <v>1475</v>
+      </c>
+      <c r="G14" t="str">
+        <v>right_only</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8" x14ac:dyDescent="0.9">
+      <c r="A16" t="str" cm="1">
+        <f t="array" ref="A16:H19">_xlfn._xlws.PY(3,0)</f>
+        <v/>
+      </c>
+      <c r="B16" t="str">
+        <v>Invoice</v>
+      </c>
+      <c r="C16" t="str">
+        <v>Vendor</v>
+      </c>
+      <c r="D16" t="str">
+        <v>Invoice_Date</v>
+      </c>
+      <c r="E16" t="str">
+        <v>Amount</v>
+      </c>
+      <c r="F16" t="str">
+        <v>Payment_Date</v>
+      </c>
+      <c r="G16" t="str">
+        <v>Amount_Paid</v>
+      </c>
+      <c r="H16" t="str">
+        <v>_merge</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8" x14ac:dyDescent="0.9">
+      <c r="A17">
+        <v>2</v>
+      </c>
+      <c r="B17" t="str">
+        <v>INV-1003</v>
+      </c>
+      <c r="C17" t="str">
+        <v>Summit Software</v>
+      </c>
+      <c r="D17" vm="2">
+        <v>46206</v>
+      </c>
+      <c r="E17">
+        <v>895</v>
+      </c>
+      <c r="F17" t="e">
+        <v>#NUM!</v>
+      </c>
+      <c r="G17" t="e">
+        <v>#NUM!</v>
+      </c>
+      <c r="H17" t="str">
+        <v>left_only</v>
+      </c>
+    </row>
+    <row r="18" spans="1:8" x14ac:dyDescent="0.9">
+      <c r="A18">
+        <v>4</v>
+      </c>
+      <c r="B18" t="str">
+        <v>INV-1005</v>
+      </c>
+      <c r="C18" t="str">
+        <v>Keystone Equipment</v>
+      </c>
+      <c r="D18" vm="3">
+        <v>46210</v>
+      </c>
+      <c r="E18">
+        <v>4750</v>
+      </c>
+      <c r="F18" t="e">
+        <v>#NUM!</v>
+      </c>
+      <c r="G18" t="e">
+        <v>#NUM!</v>
+      </c>
+      <c r="H18" t="str">
+        <v>left_only</v>
+      </c>
+    </row>
+    <row r="19" spans="1:8" x14ac:dyDescent="0.9">
+      <c r="A19">
+        <v>6</v>
+      </c>
+      <c r="B19" t="str">
+        <v>INV-1007</v>
+      </c>
+      <c r="C19" t="e">
+        <v>#NUM!</v>
+      </c>
+      <c r="D19" t="e">
+        <v>#NUM!</v>
+      </c>
+      <c r="E19" t="e">
+        <v>#NUM!</v>
+      </c>
+      <c r="F19" vm="10">
+        <v>46217</v>
+      </c>
+      <c r="G19">
+        <v>1475</v>
+      </c>
+      <c r="H19" t="str">
+        <v>right_only</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>